--- a/artfynd/A 31373-2026 artfynd.xlsx
+++ b/artfynd/A 31373-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136348844</v>
       </c>
       <c r="B2" t="n">
-        <v>96927</v>
+        <v>96930</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>136348862</v>
       </c>
       <c r="B3" t="n">
-        <v>96927</v>
+        <v>96930</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>136348849</v>
       </c>
       <c r="B5" t="n">
-        <v>98204</v>
+        <v>98207</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 31373-2026 artfynd.xlsx
+++ b/artfynd/A 31373-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136348844</v>
       </c>
       <c r="B2" t="n">
-        <v>96930</v>
+        <v>96931</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>136348862</v>
       </c>
       <c r="B3" t="n">
-        <v>96930</v>
+        <v>96931</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>136348849</v>
       </c>
       <c r="B5" t="n">
-        <v>98207</v>
+        <v>98208</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 31373-2026 artfynd.xlsx
+++ b/artfynd/A 31373-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136348844</v>
       </c>
       <c r="B2" t="n">
-        <v>96931</v>
+        <v>96936</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>136348862</v>
       </c>
       <c r="B3" t="n">
-        <v>96931</v>
+        <v>96936</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>136348855</v>
       </c>
       <c r="B4" t="n">
-        <v>58003</v>
+        <v>58005</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>136348849</v>
       </c>
       <c r="B5" t="n">
-        <v>98208</v>
+        <v>98213</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 31373-2026 artfynd.xlsx
+++ b/artfynd/A 31373-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136348844</v>
       </c>
       <c r="B2" t="n">
-        <v>96936</v>
+        <v>96938</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>136348862</v>
       </c>
       <c r="B3" t="n">
-        <v>96936</v>
+        <v>96938</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>136348849</v>
       </c>
       <c r="B5" t="n">
-        <v>98213</v>
+        <v>98215</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 31373-2026 artfynd.xlsx
+++ b/artfynd/A 31373-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136348844</v>
       </c>
       <c r="B2" t="n">
-        <v>96938</v>
+        <v>96944</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>136348862</v>
       </c>
       <c r="B3" t="n">
-        <v>96938</v>
+        <v>96944</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>136348849</v>
       </c>
       <c r="B5" t="n">
-        <v>98215</v>
+        <v>98221</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 31373-2026 artfynd.xlsx
+++ b/artfynd/A 31373-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136348844</v>
       </c>
       <c r="B2" t="n">
-        <v>96944</v>
+        <v>96946</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>136348862</v>
       </c>
       <c r="B3" t="n">
-        <v>96944</v>
+        <v>96946</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>136348849</v>
       </c>
       <c r="B5" t="n">
-        <v>98221</v>
+        <v>98223</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
